--- a/IV-ATB-Renal-Adjustment_TABLE_EN+TH.xlsx
+++ b/IV-ATB-Renal-Adjustment_TABLE_EN+TH.xlsx
@@ -803,8 +803,17 @@
 30-39: q 48 h.</t>
         </is>
       </c>
-      <c r="G5" s="32" t="n"/>
-      <c r="H5" s="32" t="n"/>
+      <c r="G5" s="43" t="inlineStr">
+        <is>
+          <t>20-29: q 48 h.
+10-19: Single dose, then individualise.</t>
+        </is>
+      </c>
+      <c r="H5" s="43" t="inlineStr">
+        <is>
+          <t>Single dose, then individualise.</t>
+        </is>
+      </c>
       <c r="I5" s="32" t="n"/>
     </row>
     <row r="6" ht="56" customHeight="1">
@@ -2155,7 +2164,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A3:I29"/>
-  <mergeCells count="44">
+  <mergeCells count="42">
     <mergeCell ref="A41:I41"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="C33:C34"/>
@@ -2176,7 +2185,6 @@
     <mergeCell ref="I14:I15"/>
     <mergeCell ref="C23:C24"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="G4:G5"/>
     <mergeCell ref="A33:A34"/>
     <mergeCell ref="I11:I13"/>
     <mergeCell ref="I4:I5"/>
@@ -2195,7 +2203,6 @@
     <mergeCell ref="C25:C27"/>
     <mergeCell ref="I25:I27"/>
     <mergeCell ref="A25:A27"/>
-    <mergeCell ref="H4:H5"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C14:C15"/>

--- a/IV-ATB-Renal-Adjustment_TABLE_EN+TH.xlsx
+++ b/IV-ATB-Renal-Adjustment_TABLE_EN+TH.xlsx
@@ -732,7 +732,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="140" customHeight="1">
       <c r="A4" s="42" t="n">
         <v>1</v>
       </c>
@@ -782,7 +782,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="112" customHeight="1">
       <c r="A5" s="32" t="n"/>
       <c r="B5" s="32" t="n"/>
       <c r="C5" s="32" t="n"/>

--- a/IV-ATB-Renal-Adjustment_TABLE_EN+TH.xlsx
+++ b/IV-ATB-Renal-Adjustment_TABLE_EN+TH.xlsx
@@ -778,7 +778,8 @@
         <is>
           <t>1. คิดตาม actual BW (adjusted ถ้า TBW มากกว่า 1.2 เท่าของ IBW)
 2. ติดตามการทำงานของไตและการได้ยิน
-3. Loading 7.5-10 mg/kg (Expert opinion)</t>
+3. Loading 7.5-10 mg/kg (Expert opinion)
+4. HDEI: ใช้ด้วยความระวังเมื่อ CrCl &lt;40 แต่ยังอาจพิจารณาได้ โดยเฉพาะผู้ป่วย severe sepsis/shock หรือติดเชื้อแบคทีเรียแกรมลบดื้อยาหลายขนาน (multidrug-resistant gram-negative)</t>
         </is>
       </c>
     </row>

--- a/IV-ATB-Renal-Adjustment_TABLE_EN+TH.xlsx
+++ b/IV-ATB-Renal-Adjustment_TABLE_EN+TH.xlsx
@@ -1541,7 +1541,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="84" customHeight="1">
       <c r="A23" s="44" t="n">
         <v>15</v>
       </c>
@@ -1586,11 +1586,12 @@
       <c r="I23" s="34" t="inlineStr">
         <is>
           <t>1. ปรับตาม Actual Body Weight (ปรับถ้า obese)
-2. ติดตามการทำงานของไตและการได้ยิน</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="56" customHeight="1">
+2. ติดตามการทำงานของไตและการได้ยิน
+3. HDEI: ใช้ด้วยความระวังเมื่อ CrCl &lt;40 แต่ยังอาจพิจารณาได้ โดยเฉพาะผู้ป่วย severe sepsis/shock หรือติดเชื้อแบคทีเรียแกรมลบดื้อยาหลายขนาน (multidrug-resistant gram-negative)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="84" customHeight="1">
       <c r="A24" s="32" t="n"/>
       <c r="B24" s="32" t="n"/>
       <c r="C24" s="32" t="n"/>
